--- a/src/attributions/attributions_ig_traj_455.xlsx
+++ b/src/attributions/attributions_ig_traj_455.xlsx
@@ -2137,25 +2137,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08727408333273601</v>
+        <v>0.251170266996418</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01642797207250347</v>
+        <v>-0.005729634026495008</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08223049834508256</v>
+        <v>-0.2338001320311467</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2164,28 +2164,28 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03891417324515582</v>
+        <v>0.350834592496012</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02488166549483367</v>
+        <v>-0.05470650959101408</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.09436539076890151</v>
+        <v>-0.2421316846422326</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007999612218006226</v>
+        <v>-0.01135175755800213</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,37 +2203,37 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-8.608517670089944e-12</v>
+        <v>-1.360286158736435e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.001748930433013935</v>
+        <v>0.01687804433338552</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.03457903056521986</v>
+        <v>-0.06529492706230006</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.04177860638056132</v>
+        <v>-0.1516085096474005</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.002327802592311289</v>
+        <v>-0.05897561282731469</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.00325257946370418</v>
+        <v>0.03447387219442311</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,16 +2257,16 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0322385386221192</v>
+        <v>-0.07121736099198751</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01939745858040779</v>
+        <v>-0.0779933966527246</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,79 +2275,79 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.08554259342875249</v>
+        <v>0.4940907161154513</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01398774979621355</v>
+        <v>-0.09809293214855774</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.06101352613117195</v>
+        <v>-0.1701085603152515</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01983739284361065</v>
+        <v>0.004922450001459674</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.03419947595479389</v>
+        <v>-0.04814710222599513</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.02981909077219066</v>
+        <v>-0.06609194137954698</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.06026684711136494</v>
+        <v>0.1074570596694414</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01410116218102058</v>
+        <v>0.1206371780891604</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01413546874850714</v>
+        <v>0.1542247966396262</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04794092056928421</v>
+        <v>0.2440974619195019</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,16 +2365,16 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.0317491031714139</v>
+        <v>-0.1342441790223444</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.005502916340310884</v>
+        <v>-0.2960803817467705</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02021450213266978</v>
+        <v>-0.1185925899703857</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.005926010609935093</v>
+        <v>-0.02267310324848723</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.04608787369803052</v>
+        <v>0.1712437360574766</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2404,202 +2404,202 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.01161434716791629</v>
+        <v>-0.2659408404476417</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01142980483733433</v>
+        <v>0.08118431702748605</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.007949442911885537</v>
+        <v>0.1205919076837682</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01187432486324526</v>
+        <v>-0.1153224913657909</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01133847450321207</v>
+        <v>-0.03223641851448382</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.04084017043401145</v>
+        <v>0.1598310484561998</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02726378902399773</v>
+        <v>-0.005748046159857452</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002129967807472999</v>
+        <v>-0.1431567600946241</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.100200347251305</v>
+        <v>0.1046102248352591</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.0148669402598718</v>
+        <v>-0.06240973617294311</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.02170968386930312</v>
+        <v>0.1022165880552528</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01331238477748404</v>
+        <v>0.187246743870522</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01537334084896861</v>
+        <v>0.004032378236155898</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01650015554441375</v>
+        <v>-0.01258163483751938</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.03981623509451866</v>
+        <v>-0.1131664058380312</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.002403043101140439</v>
+        <v>-0.1080365491357565</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.008125011946469016</v>
+        <v>-0.1056032120741241</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001479753386309921</v>
+        <v>0.1130126850177235</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.001804926691556863</v>
+        <v>0.008949843422275684</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.02562075530765663</v>
+        <v>-0.1232214893875168</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.05181487772292677</v>
+        <v>0.1238460893456328</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01315912561089471</v>
+        <v>-0.1325801150331161</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,100 +2608,100 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.008650347432055618</v>
+        <v>-0.06200225515768042</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03731126965678611</v>
+        <v>0.148741146753773</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01317345208808128</v>
+        <v>-0.1569045170425589</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.03031110527004939</v>
+        <v>-0.01883956572722398</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.01272503737130856</v>
+        <v>-0.01011768040825744</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.001453011381188064</v>
+        <v>0.09166972465231846</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.006704718076991463</v>
+        <v>0.07763084597757493</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.06437703176086719</v>
+        <v>0.132992861674407</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.03628349032913704</v>
+        <v>0.01333658444374095</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.006196896051943147</v>
+        <v>0.1345907095295649</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2536977471800035</v>
+        <v>0.2884611740343247</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1001145504904244</v>
+        <v>-0.1149493648768789</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1184419826617814</v>
+        <v>-0.04064587260593161</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1535927038812772</v>
+        <v>0.2689083774543234</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05327147237775188</v>
+        <v>-0.09646962760300637</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1238259403166354</v>
+        <v>-0.09160422762374229</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,73 +2760,73 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0135512665319853</v>
+        <v>0.01613336667641463</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.00844455339361224</v>
+        <v>-0.005258873131394953</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00352095190300312</v>
+        <v>-0.0007975673228436971</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07066940238318888</v>
+        <v>-0.05644085107289745</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02724283184260177</v>
+        <v>-0.09479543196021198</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.07417046938767531</v>
+        <v>-0.08774459627850431</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01088620113800968</v>
+        <v>0.1080272378035527</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.04066507844130653</v>
+        <v>-0.03004675703381298</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08831362761948509</v>
+        <v>0.05482575501591838</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,34 +2835,34 @@
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3309384221161172</v>
+        <v>0.2579228296824648</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.02710014973629501</v>
+        <v>-0.1191824989257469</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.121482436043817</v>
+        <v>-0.1339498285523003</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00119180359691339</v>
+        <v>-0.01417404266462518</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.08286590972697597</v>
+        <v>-0.02127464206819138</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.112598004991746</v>
+        <v>-0.01344707985796679</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,31 +2889,31 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1701695321368769</v>
+        <v>-0.0140526474323737</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.05068906073211055</v>
+        <v>0.042991732177155</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1868513015828584</v>
+        <v>0.06994107443455103</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,25 +2925,25 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2315950019382538</v>
+        <v>0.2517005454795837</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.00614328460294165</v>
+        <v>-0.1242803391278021</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01109952078419985</v>
+        <v>-0.02564708935849802</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,16 +2952,16 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.07287424908356276</v>
+        <v>-0.1419777812723971</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02835033909718585</v>
+        <v>0.09989292602506659</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01195100511374847</v>
+        <v>0.0251325834071241</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2979,19 +2979,19 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.03744088966045861</v>
+        <v>-0.0765256492383226</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06953436348124194</v>
+        <v>0.09834055610384984</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1502428576763397</v>
+        <v>0.06042397373729187</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -3003,19 +3003,19 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.0478665448784884</v>
+        <v>-0.1489497993367147</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.04887520278281549</v>
+        <v>0.1127274814772797</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.03058978567370953</v>
+        <v>0.03281906616300381</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.00189601566839918</v>
+        <v>-0.006833226881778965</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.04143304171603877</v>
+        <v>0.02568062642754665</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.01121300322538755</v>
+        <v>-0.09884865118482232</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
@@ -3060,73 +3060,73 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.07906244752860028</v>
+        <v>-0.08981644098863412</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01758770606360126</v>
+        <v>0.04743348669404088</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03316153770247207</v>
+        <v>-0.0253334594276128</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01110658053119638</v>
+        <v>0.04907773697759193</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.05586838202985328</v>
+        <v>0.04219731324552275</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03755520192209984</v>
+        <v>-0.01962862938332553</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04705603493390475</v>
+        <v>-0.08897135817017508</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.01416116182402654</v>
+        <v>0.1091638755631734</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.1180312334767065</v>
+        <v>0.01750414127978361</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3141,70 +3141,70 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.05210053377239574</v>
+        <v>-0.09397191800552315</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.02971979931139701</v>
+        <v>0.07490643323699578</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.002185663754624066</v>
+        <v>-0.02239117231542477</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.04989131449314883</v>
+        <v>-0.1538410142198574</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.05036606182170809</v>
+        <v>0.1209307581926411</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.03781196291699544</v>
+        <v>0.01255094291729452</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.04016113635462819</v>
+        <v>-0.06831309398613818</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.109010206267746</v>
+        <v>-0.03723518865519093</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0189320200059124</v>
+        <v>0.04883152186969868</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3213,84 +3213,84 @@
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.06621812078109421</v>
+        <v>0.0257197908629569</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.03880440984762812</v>
+        <v>0.1703297534007661</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.05301276258563901</v>
+        <v>-0.04622256461426147</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.002044228204135527</v>
+        <v>-0.1163691371459283</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.02053717539318418</v>
+        <v>0.0739054410175366</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02040776730797569</v>
+        <v>0.04456430410368178</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02887801450238349</v>
+        <v>0.02961228767504128</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01365143524629087</v>
+        <v>-0.01971817990975711</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,22 +3302,22 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003162173690686853</v>
+        <v>0.07513815315299649</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.03793284252861227</v>
+        <v>0.01869563584150626</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02191533474832246</v>
+        <v>-0.02244699364770796</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001264890983737572</v>
+        <v>-0.0006125458339964011</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,16 +3341,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0007845400952518819</v>
+        <v>-0.006487828124496789</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002162647457495659</v>
+        <v>-0.0002773426498883815</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>-0</v>
@@ -3359,25 +3359,25 @@
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02965569108510239</v>
+        <v>-0.01849652765281223</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04745117381651875</v>
+        <v>-0.07213556575909648</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.01241889489399559</v>
+        <v>-0.0208902744230417</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.002277153390286133</v>
+        <v>0.01253713047106295</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,37 +3395,37 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0236038736586186</v>
+        <v>-0.01154502017985267</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.00607513533114957</v>
+        <v>-0.0225942294001267</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05341396926375721</v>
+        <v>0.08949086837605962</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01210765446658647</v>
+        <v>-0.01622122909728142</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0115221761452993</v>
+        <v>-0.01301481356548836</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3434,28 +3434,28 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.006527634654873844</v>
+        <v>-0.007835880498342114</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03528382965739098</v>
+        <v>-0.01697606876258672</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.005237305750544502</v>
+        <v>-0.005448087903432223</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,52 +3464,52 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04925292471064071</v>
+        <v>0.02154655607099386</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01598384287812647</v>
+        <v>0.04558025092963025</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01555462159884095</v>
+        <v>0.0383046756209796</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01381715535965055</v>
+        <v>0.04892977257710765</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.02956769536606904</v>
+        <v>0.001089831271638598</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01987478884447434</v>
+        <v>-0.03713817073418684</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0007376304437758888</v>
+        <v>-0.0126208304882997</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0006972099360138721</v>
+        <v>-0.003853449858669067</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.008089288705127005</v>
+        <v>0.02732774980050247</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>-0</v>
@@ -3545,22 +3545,22 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.005256418262567416</v>
+        <v>-0.03952688132979931</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.01753311177417032</v>
+        <v>0.05892558060544821</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01660625448424183</v>
+        <v>0.02460895635349859</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.007807138392368874</v>
+        <v>-0.01635502961560219</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001267521328222969</v>
+        <v>-0.006826884979656016</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.006151923025770901</v>
+        <v>0.0239383043008807</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3602,19 +3602,19 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.002302067932934519</v>
+        <v>-0.01934555949685693</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0001965281450093154</v>
+        <v>-0.001648242479316711</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.03558674865230877</v>
+        <v>-0.002414298322362879</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.005972733035155777</v>
+        <v>-0.01713274755017996</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03033955024633695</v>
+        <v>0.0008831928838196124</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.01072042470131592</v>
+        <v>0.0351610880519305</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3653,82 +3653,82 @@
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.00966380674328368</v>
+        <v>-0.01484192945265513</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.007042515143547892</v>
+        <v>0.01200461058029387</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.01421921122415507</v>
+        <v>0.03102918254028177</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.006182345175268205</v>
+        <v>-0.01281296833191899</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001220347905559394</v>
+        <v>-0.02618769675558844</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.007665360525104423</v>
+        <v>0.003755362460266306</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.001060757007181838</v>
+        <v>0.000217356592837077</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.02449585024724498</v>
+        <v>0.00169568401168892</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.04000771745832816</v>
+        <v>0.01074686573985854</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>0</v>
@@ -3737,19 +3737,19 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.009111891911496965</v>
+        <v>-0.02033355073304669</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.0003514428897889035</v>
+        <v>-0.01241331299753816</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01083619365570031</v>
+        <v>0.01819546665941674</v>
       </c>
       <c r="FD6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-8.704224322433244e-05</v>
+        <v>-0.0241255063093738</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,37 +3773,37 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02059793530724213</v>
+        <v>0.01816528000705541</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01703189754883701</v>
+        <v>0.000374767474319222</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.01028013304629756</v>
+        <v>0.01516118538658343</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001239959569143374</v>
+        <v>0.003950961539922527</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.019147148408932</v>
+        <v>-0.04714854920626328</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,16 +3812,16 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02834582021260933</v>
+        <v>0.01282573292887859</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,7 +3830,7 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.006591042892524724</v>
+        <v>0.01339791107638279</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1834531496146151</v>
+        <v>0.07796771566826662</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02530348903479894</v>
+        <v>-0.03555970333093553</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03229954023722099</v>
+        <v>-0.009680621366466753</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08569597519506916</v>
+        <v>0.1198548836359288</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1047368912760724</v>
+        <v>-0.04097469588391888</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.05103869192093132</v>
+        <v>-0.008973059903508501</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01919771833335716</v>
+        <v>-0.004435378343007301</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.006576688860824287</v>
+        <v>-0.01267883476697952</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.000778544395738913</v>
+        <v>0.0002918671453187451</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.08051184714177007</v>
+        <v>-0.02158729334456777</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02975766768356486</v>
+        <v>-0.02100799144659085</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,55 +3946,55 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.02108054928068648</v>
+        <v>-0.001656646738382432</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04759251823643305</v>
+        <v>0.02745794585196535</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02897671227156706</v>
+        <v>-0.009355145493137344</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0194098762454724</v>
+        <v>-0.008690462914650558</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2267780846053862</v>
+        <v>0.1076299439439627</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09345464300714687</v>
+        <v>-0.009989291128610892</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0008497958895909365</v>
+        <v>0.01321123428432988</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0345181976370155</v>
+        <v>-0.009765547969643927</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.08311677299622233</v>
+        <v>-0.02889378383821725</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,70 +4027,70 @@
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.00801337168845543</v>
+        <v>-0.003828350093475072</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02181157239145136</v>
+        <v>0.01529588327833786</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1369563829714847</v>
+        <v>0.05131174817075698</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02089809592243562</v>
+        <v>0.01584425062787901</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1686248808896383</v>
+        <v>0.07094535168807778</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.001843402113623602</v>
+        <v>-0.02965106221040454</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01881459863738442</v>
+        <v>-0.02250669887369056</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0455352542482594</v>
+        <v>-0.03180731081212063</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0009466797761744304</v>
+        <v>0.01180595042717071</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.03920780030843358</v>
+        <v>0.01688987519847586</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.03092036293162503</v>
+        <v>-0.05627683299452362</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.04332456371227232</v>
+        <v>0.007934219367424521</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.01279349963615829</v>
+        <v>0.02434347679238412</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04168870561601391</v>
+        <v>-0.03286179952141372</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.008912156742622714</v>
+        <v>0.005974000181374497</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4165,22 +4165,22 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03460543977350412</v>
+        <v>0.01594619948058992</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.147770312927533</v>
+        <v>-0.02801327408877361</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0676737216749513</v>
+        <v>-0.01587522538597989</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,97 +4189,97 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.01652399876392523</v>
+        <v>-0.006399807810695321</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.01143803225723971</v>
+        <v>-0.01560195002961537</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.01410640580580428</v>
+        <v>0.007531303323073454</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.02110439183138373</v>
+        <v>-0.02996736020437295</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00398493899617621</v>
+        <v>0.01730736079674802</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01466034343596417</v>
+        <v>0.006465004823699162</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01042384257912918</v>
+        <v>-0.01563804235089978</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0003555256258888585</v>
+        <v>-0.03033785152161701</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03952493229143496</v>
+        <v>0.006289746807903841</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.04651012028297122</v>
+        <v>0.009692305211101085</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.06935831244842429</v>
+        <v>-0.007035568292838913</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.001642858790079652</v>
+        <v>0.01048829340441536</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.02621514815887827</v>
+        <v>0.001397292719030878</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.055482921966187</v>
+        <v>-0.03729248505517722</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.003408975273563518</v>
+        <v>0.001563704031629238</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02110726496964106</v>
+        <v>0.01631556464481441</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04922140673439589</v>
+        <v>-0.02410629856742073</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01879838269092638</v>
+        <v>0.005876784235282154</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.04774793572183478</v>
+        <v>0.04845428514884641</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.07775213529239468</v>
+        <v>0.01565678943647969</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,10 +4369,10 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02073026793540261</v>
+        <v>-0.01833139486379015</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,13 +4381,13 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.00224028034265096</v>
+        <v>0.001309413709939412</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.07794478820272563</v>
+        <v>-0.01724160102486808</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03029943215652521</v>
+        <v>9.538174737257047e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4525616042039332</v>
+        <v>0.1818188895542033</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2095715192366093</v>
+        <v>-0.1141685936211475</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0007206496988728582</v>
+        <v>-0.04414750352001035</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5009,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2843361497167144</v>
+        <v>0.1874724445780349</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2349990485650978</v>
+        <v>-0.1731609527152248</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1078920687824776</v>
+        <v>-0.09479624438931866</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.05209956772404248</v>
+        <v>0.03435450737957078</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01016140194662555</v>
+        <v>-0.005695624071800428</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0248783133499935</v>
+        <v>-0.02426426435741078</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1957574315964463</v>
+        <v>-0.01081944074114031</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.0134655659552875</v>
+        <v>-0.06550655202413405</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03117353478373372</v>
+        <v>-0.0931457441395557</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.005926184768991423</v>
+        <v>0.1179653201319669</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.06048394321124766</v>
+        <v>-0.07219179360144407</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1214589813684086</v>
+        <v>0.04693378899780383</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,22 +5120,22 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4584113511712612</v>
+        <v>0.1607863855045777</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0313199327274358</v>
+        <v>-0.04350940371883728</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2084320656771185</v>
+        <v>-0.17436428563834</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -5147,16 +5147,16 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.02913952701584126</v>
+        <v>-0.03896207212391053</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1101161142388824</v>
+        <v>-0.01098508289171771</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1936414251106675</v>
+        <v>0.008677949492129534</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.238396114713154</v>
+        <v>0.04845913138122971</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.03622714819140422</v>
+        <v>0.01901131679626535</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.2187228750737418</v>
+        <v>0.03903713759603138</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2930846034555494</v>
+        <v>0.2041835745274001</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.008684557079408598</v>
+        <v>-0.1464723154040762</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.05522302104868417</v>
+        <v>-0.05946699527871951</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,25 +5228,25 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1117100547358331</v>
+        <v>-0.06557681502531046</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.008912384477767021</v>
+        <v>0.09590052620740493</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02407903334681239</v>
+        <v>0.02273484472228038</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.1061874716683512</v>
+        <v>-0.06353860670173198</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1755839663857172</v>
+        <v>0.2055552450796011</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.07716816255648695</v>
+        <v>0.0795822790969945</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,25 +5282,25 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.07167951026623487</v>
+        <v>-0.04776072099160218</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.03726018908417419</v>
+        <v>0.1049791206187382</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001221891375365541</v>
+        <v>0.04169677138151996</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01477003629271221</v>
+        <v>-0.006177765399290005</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.05004308960866083</v>
+        <v>0.0106806511064243</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05205470799975383</v>
+        <v>-0.02684484708204483</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,103 +5336,103 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.100284143284993</v>
+        <v>-0.08497070728814904</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.02551314661329419</v>
+        <v>0.05812747809892339</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01995869567128755</v>
+        <v>0.04222911867646316</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.01800837970583423</v>
+        <v>0.0009227995873839891</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.03364050558838224</v>
+        <v>0.03529926565157732</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.009477513605028624</v>
+        <v>-0.03517550389222311</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.02864114949901417</v>
+        <v>0.02053451738756601</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03574097723898039</v>
+        <v>0.07293620345089291</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05990818958923565</v>
+        <v>0.0339773632948314</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.117795648951158</v>
+        <v>-0.06711114059801131</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.06518878772820227</v>
+        <v>-0.08610671938260166</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0069341892011472</v>
+        <v>0.0008609184389190848</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,22 +5444,22 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.08284407016374885</v>
+        <v>-0.06560339274606669</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02169186238053448</v>
+        <v>0.115771461766371</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.02920428139046604</v>
+        <v>0.01942262907373808</v>
       </c>
       <c r="FC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,16 +5471,16 @@
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.04531936573155553</v>
+        <v>-0.02728221482156481</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04935948847862767</v>
+        <v>0.0273688925500765</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01403760502928386</v>
+        <v>-0.04900645810053676</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,64 +5489,64 @@
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.09568911711101095</v>
+        <v>0.02555138159267326</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.09561647183709027</v>
+        <v>0.1083172659724898</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1391517482203208</v>
+        <v>-0.08956154257530838</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.05375569386018141</v>
+        <v>-0.003681330229880683</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.09778277086168013</v>
+        <v>0.0359874165411276</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1.40434735419614</v>
+        <v>0.2166308652137119</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2746927272634067</v>
+        <v>-0.4133636097566425</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1923304221497075</v>
+        <v>-0.05935534161379416</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01273381484807137</v>
+        <v>0.03266332991849714</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8810205909955722</v>
+        <v>0.1513257576669099</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3156532833873869</v>
+        <v>-0.5384848854801706</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3597844008534927</v>
+        <v>-0.1507421588590646</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,133 +5599,133 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.004667686302193341</v>
+        <v>0.005406724832168579</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2231583204934445</v>
+        <v>0.07183249061907787</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1234457677730412</v>
+        <v>-0.09269167294957052</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.05078104297452805</v>
+        <v>-0.1687192805725892</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01643073257284963</v>
+        <v>0.002509770700529016</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1985237331644376</v>
+        <v>-0.1245943263984791</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03294567828258774</v>
+        <v>-0.001909687158373174</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1556958380053927</v>
+        <v>-0.1310425487006275</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.005865709986457513</v>
+        <v>0.02611898460631199</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.06644471403928286</v>
+        <v>0.1390324782884145</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.1172293621897696</v>
+        <v>-0.09447024200845397</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1469245281305787</v>
+        <v>-0.004794989946702521</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.06187555353873133</v>
+        <v>0.003366018603136582</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.111871234401161</v>
+        <v>0.2200952573750174</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.06375594977947749</v>
+        <v>-0.1339407351776407</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2556228118438695</v>
+        <v>-0.329710683648273</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.204001450534866</v>
+        <v>-0.04950742717239118</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.2159859754030614</v>
+        <v>-0.0707849959853995</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1927100573298218</v>
+        <v>-0.07271863233210214</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.5947656677696518</v>
+        <v>0.01520443073838953</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-7.402500480402608e-11</v>
+        <v>4.856881536264186e-11</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5504826297622997</v>
+        <v>0.1188107695666146</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.2744363850612495</v>
+        <v>0.1848113698822994</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.3180745279211847</v>
+        <v>0.01717627428934376</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.08781687709896276</v>
+        <v>0.02285016753536343</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,43 +5770,43 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.731713251873168</v>
+        <v>0.2460600206754774</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.08285379673986194</v>
+        <v>-0.3992066638580826</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.06401264151047729</v>
+        <v>-0.2565660034761309</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.02472883111732285</v>
+        <v>-0.08013887284148061</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.3073041286946662</v>
+        <v>-0.04841088823167604</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01161449595119119</v>
+        <v>0.2788015120288089</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.06943727537952916</v>
+        <v>0.05112174068078967</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,160 +5815,160 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.0107506542579479</v>
+        <v>-0.06874003076395305</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1980116337499614</v>
+        <v>-0.0009322957515089351</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.2682195238786826</v>
+        <v>0.3032760336688795</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1545499334811495</v>
+        <v>0.3299364084868117</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.07424497360481973</v>
+        <v>0.01249771567483863</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.2369816694955902</v>
+        <v>-0.03969638951157669</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.09601744750063285</v>
+        <v>0.3055993129606555</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.08793782087166731</v>
+        <v>0.06830741455640689</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.01453542573232243</v>
+        <v>-0.05934903170111708</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.2672100139244124</v>
+        <v>-0.03928107237012821</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.06951062577391338</v>
+        <v>0.09207840588098208</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01021119817543879</v>
+        <v>0.00401296319764901</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.02375494147771005</v>
+        <v>-0.09972371121131049</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.214822269571879</v>
+        <v>-0.04670603776207297</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.01284780929059091</v>
+        <v>0.1328943315787044</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.08561871147084112</v>
+        <v>-0.08286050745335607</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1347339966269558</v>
+        <v>0.1930866735414073</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.07505988501181697</v>
+        <v>0.02231670095096437</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.03252723109543783</v>
+        <v>0.1074889094262292</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.2597783224171851</v>
+        <v>-0.1521168969005584</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.05983533164884421</v>
+        <v>0.2646528024829966</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.1943339201569239</v>
+        <v>0.06122196576015896</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.02999930360168831</v>
+        <v>0.2550452377475914</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02889585271730435</v>
+        <v>0.0510428947536335</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.03768355476022561</v>
+        <v>-0.05755644986629172</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,97 +5986,97 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.24387606178247</v>
+        <v>-0.06275247643839706</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1085330712501782</v>
+        <v>0.2607783269085527</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.1603611781910579</v>
+        <v>-0.01693756081904149</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.1348873207002306</v>
+        <v>-0.06608701552574357</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.2560760082727601</v>
+        <v>-0.06521078306263818</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.05714347264563182</v>
+        <v>0.3404495208534663</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.02650379642203263</v>
+        <v>0.06018652783506652</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.01750968347530383</v>
+        <v>-0.06789873459024964</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.02489328163575895</v>
+        <v>-0.01919438910583559</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.147345484935715</v>
+        <v>-0.1345376817504934</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.09107903377315339</v>
+        <v>0.04215576553161735</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.004500819176213483</v>
+        <v>-0.0482584866304199</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.2105743494839237</v>
+        <v>0.07428190974856538</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.1955568602357961</v>
+        <v>0.2148292654366893</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.2236231643255221</v>
+        <v>-0.1960666623101192</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
@@ -6085,34 +6085,34 @@
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.1382752547903637</v>
+        <v>-0.2101320730974006</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1442304624216527</v>
+        <v>-0.003350155198784498</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.1051998949251333</v>
+        <v>0.1618079710383552</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1287593793242446</v>
+        <v>-0.08109900102970238</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3311740214047476</v>
+        <v>0.5243234762542949</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07841148363124359</v>
+        <v>-0.01064627228550998</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3617152387031586</v>
+        <v>-0.4913111497179324</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,25 +6150,25 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2842572047208688</v>
+        <v>0.7402234465722494</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.07309789223131173</v>
+        <v>-0.2153998705333559</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3380230453620474</v>
+        <v>-0.5147229824488149</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03306195982265273</v>
+        <v>0.109737448698743</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.02037249780373158</v>
+        <v>-0.1851536057586231</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001943583326315395</v>
+        <v>-0.05700267413960608</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0421461716095435</v>
+        <v>0.02635841254330701</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.002606785900232764</v>
+        <v>-0.3651569238098358</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.01181233025982084</v>
+        <v>-0.06873350343096327</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04997121231415386</v>
+        <v>0.09326354380708693</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.009735079260320998</v>
+        <v>-0.1534903110149485</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.05571700436251398</v>
+        <v>-0.0852830521483437</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,28 +6255,28 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2519273917613636</v>
+        <v>0.7066007380736219</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01569699780960623</v>
+        <v>-0.1021368978998541</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.09010855627469896</v>
+        <v>-0.1077223952403319</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
@@ -6285,61 +6285,61 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1135099069960811</v>
+        <v>-0.09404324971824045</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.119286972494967</v>
+        <v>-0.06681456807514084</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.1747615295122278</v>
+        <v>-0.2140965012369836</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1732452522112836</v>
+        <v>0.2674762286470244</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.08703888648989755</v>
+        <v>0.2651436875973494</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02075405342517977</v>
+        <v>0.1571506287707037</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1611521119862398</v>
+        <v>0.5470542180996041</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.00623100833578922</v>
+        <v>-0.1143300001251765</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.06186600130724969</v>
+        <v>-0.2117416812309338</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,76 +6366,76 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.05713351304847241</v>
+        <v>-0.1700015933629745</v>
       </c>
       <c r="CF11" t="n">
         <v>0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.003217794029603526</v>
+        <v>0.02553393970739959</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.07334354640099744</v>
+        <v>0.1773778791818446</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.07044021655175409</v>
+        <v>-0.4064868519537503</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.03222949797640067</v>
+        <v>0.08423133767685989</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.02861847300483875</v>
+        <v>0.09752937310616501</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.03780528810257929</v>
+        <v>-0.1417311502961482</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.006700348586245428</v>
+        <v>-0.01426622310391354</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.07023683174835775</v>
+        <v>0.1666165955001404</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,19 +6447,19 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.05668013563421229</v>
+        <v>-0.1722956784620544</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03331809078865954</v>
+        <v>-0.2205361036187873</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.007658424426626217</v>
+        <v>-0.04286613600064305</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,67 +6468,67 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04762386112843522</v>
+        <v>-0.05551840806446055</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03425384188258739</v>
+        <v>-0.01089445323327255</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.04202691227419766</v>
+        <v>-0.04774164363905894</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.005715892090499139</v>
+        <v>0.08528318479052883</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.01792313735040392</v>
+        <v>-0.003022441085949246</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.003385811091893396</v>
+        <v>0.0940448417701394</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.007195419934785674</v>
+        <v>0.001888175848501084</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
@@ -6537,37 +6537,37 @@
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0002420695405342115</v>
+        <v>-0.1331378066784831</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.05931819074327837</v>
+        <v>0.1541155850601059</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.008049231521300807</v>
+        <v>-0.009935991288378821</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01605283363813044</v>
+        <v>-0.1213278328296259</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.06097569062578709</v>
+        <v>0.1599417747947763</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
@@ -6576,58 +6576,58 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.03354442531295541</v>
+        <v>-0.1906989887828537</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.008417622215874766</v>
+        <v>-0.04201365021882553</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.07347999510831311</v>
+        <v>0.1584862518483233</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03468044562529789</v>
+        <v>-0.2151872760250752</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03357610539364666</v>
+        <v>0.2053963379762002</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0439070771799483</v>
+        <v>0.06662566794596564</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,52 +6636,52 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0195448485744537</v>
+        <v>0.02893448854558257</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.01094710576993349</v>
+        <v>-0.02956610383241971</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04895390601343189</v>
+        <v>0.07218145477404672</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.06286557142615731</v>
+        <v>-0.1046349267569978</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.04532711341646742</v>
+        <v>0.1014560309403644</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5474600694180309</v>
+        <v>0.2832627075336242</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3142296359355014</v>
+        <v>-0.120099534619227</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1111768161991776</v>
+        <v>-0.07296207312474401</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,22 +6719,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3893306473248145</v>
+        <v>0.2997664034348083</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2823483688390314</v>
+        <v>-0.175729101687468</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1892434353101057</v>
+        <v>-0.1278053183624776</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6743,22 +6743,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1512831097811523</v>
+        <v>0.06825388307726331</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.00110870302838553</v>
+        <v>-0.0228394049998393</v>
       </c>
       <c r="W12" t="n">
-        <v>0.06007289297403032</v>
+        <v>-0.02945975698426663</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,55 +6770,55 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1886684673510678</v>
+        <v>-0.012733459280522</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01357904732796818</v>
+        <v>-0.1450784975993479</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.03319466694514887</v>
+        <v>-0.1309035486862905</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04671097522548482</v>
+        <v>0.1381570874553242</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04224725894781146</v>
+        <v>-0.06944636522454417</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.07855889116374386</v>
+        <v>0.06107912588262472</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,19 +6827,19 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4362605965615064</v>
+        <v>0.2019672420364975</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01116493910601764</v>
+        <v>-0.01109235298404431</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1103748880583686</v>
+        <v>-0.1268155118677297</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -6851,19 +6851,19 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05318127362939452</v>
+        <v>-0.0279998631296894</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1422247541599586</v>
+        <v>-0.06987868468928532</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.3001211825181319</v>
+        <v>-0.04397141404562057</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1748662949493205</v>
+        <v>0.04993203413738653</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.03219698751746026</v>
+        <v>0.005112810317637568</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1371008931958247</v>
+        <v>0.1325579109056038</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2833000504897013</v>
+        <v>0.2521138062203349</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.001723980831630413</v>
+        <v>-0.06470946405196495</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.09468900979588295</v>
+        <v>-0.03108471048997962</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1273220614900842</v>
+        <v>-0.1007111298344159</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0202097623910751</v>
+        <v>0.0859019231140018</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.02096460529397082</v>
+        <v>0.04203026951151564</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6962,25 +6962,25 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.08970371142584772</v>
+        <v>-0.1520502302406585</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.2018668871578718</v>
+        <v>0.2304195326917822</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07757213382219579</v>
+        <v>0.0765858728759756</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
@@ -6989,16 +6989,16 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.08014842277705304</v>
+        <v>-0.07497337571357336</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.05134592866777485</v>
+        <v>0.09147580025933377</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01693548257390847</v>
+        <v>0.05110771889549044</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7007,28 +7007,28 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.09142721608241981</v>
+        <v>-0.02102771571453609</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0434009129480203</v>
+        <v>-0.007576270338918487</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04075313634378745</v>
+        <v>-0.05568968220524435</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7043,52 +7043,52 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.09824345125328092</v>
+        <v>-0.1085818407962971</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.05107184560423659</v>
+        <v>0.06178575788261335</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.06061105047193494</v>
+        <v>0.02943834822561867</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01808506948855686</v>
+        <v>0.04021073965202102</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.07678395769587991</v>
+        <v>-0.03472472885813117</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02840548314993743</v>
+        <v>-0.05652714733753196</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,49 +7097,49 @@
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.04676898778567689</v>
+        <v>-0.01126113244197745</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.06289169684395203</v>
+        <v>0.0820811071701421</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.09501474258472511</v>
+        <v>0.08574042459007526</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.086895913684837</v>
+        <v>-0.06902927955714197</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0506738221600419</v>
+        <v>0.05076405862027345</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04396634470939179</v>
+        <v>-0.002557934939880309</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,76 +7151,76 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.09178082317257336</v>
+        <v>-0.1072098748569984</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.04418820513863073</v>
+        <v>0.106013159646552</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.005697035011316018</v>
+        <v>0.03368344604292533</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.02548647476953748</v>
+        <v>-0.02690053546192389</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.07504655734713678</v>
+        <v>0.01882887872258069</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.06329610171058175</v>
+        <v>-0.06216466951219243</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
         <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.06261040991692036</v>
+        <v>-0.009097278152818196</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.09405001315469029</v>
+        <v>0.06037345080799316</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.05780427000402248</v>
+        <v>-0.1248020498479121</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
@@ -7229,51 +7229,51 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.01664828258603311</v>
+        <v>-0.06974789796205924</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.07512935962109221</v>
+        <v>0.02371604764891616</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.5585706087508591</v>
+        <v>-0.2120211125419555</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.305037794545877</v>
+        <v>-0.03457127797324539</v>
       </c>
       <c r="F13" t="n">
-        <v>1.230148246554264</v>
+        <v>0.3556419270350358</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7288,73 +7288,73 @@
         <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4386883047183827</v>
+        <v>-0.2345964293735571</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0579478752331526</v>
+        <v>0.06976962439015756</v>
       </c>
       <c r="O13" t="n">
-        <v>1.079889317997603</v>
+        <v>0.336226001624005</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R13" t="n">
         <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01639976991250501</v>
+        <v>-0.1162143679671053</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3409987658774473</v>
+        <v>0.148348619883739</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1452850152033824</v>
+        <v>0.0494222908489155</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.02272724667646395</v>
+        <v>0.03248547008285316</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.08199118274164136</v>
+        <v>0.3046233248318101</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.08217418998600391</v>
+        <v>0.1922762836632221</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,22 +7369,22 @@
         <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.04480995386979574</v>
+        <v>-0.1031449146902327</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.04080987087811062</v>
+        <v>-0.07196116194034408</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1144064361780784</v>
+        <v>0.1173908410115539</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7393,22 +7393,22 @@
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.2444691259638775</v>
+        <v>-0.3015985923984331</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.3253292734102067</v>
+        <v>0.04645390041871837</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.6049166431062241</v>
+        <v>0.1115072943911263</v>
       </c>
       <c r="AZ13" t="n">
         <v>-0</v>
@@ -7417,13 +7417,13 @@
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.255980599125687</v>
+        <v>0.1228378013096991</v>
       </c>
       <c r="BE13" t="n">
         <v>-0</v>
@@ -7432,70 +7432,70 @@
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.08461084736840797</v>
+        <v>0.2733261772954348</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.2786879197571853</v>
+        <v>0.1797854520581887</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.1502027507153685</v>
+        <v>0.009949444638999598</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.006028538269777613</v>
+        <v>-0.08697965035956529</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.009110929867189938</v>
+        <v>-0.03713136279900325</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.2481060087505141</v>
+        <v>-0.2876191560582195</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
         <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.22858321582877</v>
+        <v>0.04792917757230333</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.510617173158064</v>
+        <v>0.206649495111913</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,49 +7504,49 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.09748766879597667</v>
+        <v>0.09418382758389061</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.0740025584352472</v>
+        <v>-0.02380859048006611</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.2419269696073282</v>
+        <v>-0.1104555466000964</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.02446734916787508</v>
+        <v>0.1665311347970032</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.3138544615957214</v>
+        <v>-0.3873677123239</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.03682940341286094</v>
+        <v>-0.201467701049004</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7558,22 +7558,22 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.07137955580753041</v>
+        <v>0.07905600730097347</v>
       </c>
       <c r="CX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY13" t="n">
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.07330210157298124</v>
+        <v>-0.02067438992000652</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0.2355289612982539</v>
+        <v>-0.1024490189535597</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7585,73 +7585,73 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.02817029938590767</v>
+        <v>0.03517141052271614</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.177788429645574</v>
+        <v>0.1402458944691045</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.03896905466079046</v>
+        <v>-0.002689689398926152</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.07722137972246332</v>
+        <v>0.0394548533657833</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.1438351912647222</v>
+        <v>0.01807381203458621</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.1362276682903147</v>
+        <v>-0.09765827717396701</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.03710225754049851</v>
+        <v>-0.05819407902508342</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.08004489403221751</v>
+        <v>0.04402172711025597</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.1576237667861878</v>
+        <v>-0.04815030696075974</v>
       </c>
       <c r="EC13" t="n">
         <v>0</v>
@@ -7660,25 +7660,25 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.1322020367527788</v>
+        <v>0.02766924129577447</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.1189175944029144</v>
+        <v>0.02210093892715938</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.1667599425875176</v>
+        <v>-0.01509136238255793</v>
       </c>
       <c r="EL13" t="n">
         <v>0</v>
@@ -7693,49 +7693,49 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.04892910907308666</v>
+        <v>-0.002337432362138696</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.08046491078043658</v>
+        <v>0.02257863417868899</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.1238000760681661</v>
+        <v>-0.08885903167284401</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.06896271472077815</v>
+        <v>0.09652431631956426</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.1333757948638803</v>
+        <v>-0.01407899121019828</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0.2211982836320849</v>
+        <v>-0.1034417213890698</v>
       </c>
       <c r="FD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0824769277555908</v>
+        <v>0.1421800281542409</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.06698771764917452</v>
+        <v>-0.02988275146475418</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0477941058298848</v>
+        <v>0.03407310697234481</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.03901540708230322</v>
+        <v>-0.04049984012739427</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,43 +7783,43 @@
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.1726368784344654</v>
+        <v>-0.05179599815488872</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.05873442334438549</v>
+        <v>0.07126348158029375</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.07054578186206231</v>
+        <v>0.08698763309785364</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-8.911127609833761e-05</v>
+        <v>0.0003071904692661998</v>
       </c>
       <c r="GE13" t="n">
         <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7827,61 +7827,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.001124989522622425</v>
+        <v>-0.03634625273881832</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1486044598255142</v>
+        <v>0.8461304140396975</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1273781967433796</v>
+        <v>-0.2085986009640506</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01175756419475885</v>
+        <v>0.0361707527325594</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.07713646637712979</v>
+        <v>1.106964268368492</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1479104651983602</v>
+        <v>-0.07226728211647999</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02585305269176804</v>
+        <v>0.009135946300668924</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -7890,16 +7890,16 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.07859451321429367</v>
+        <v>0.1068598184144405</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01125640965887103</v>
+        <v>0.3089470716431535</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
@@ -7908,7 +7908,7 @@
         <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0889781603272696</v>
+        <v>-0.07216724326524314</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -7917,52 +7917,52 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0923330417826031</v>
+        <v>-0.1716493741243935</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09023998354104427</v>
+        <v>-0.4716776288697133</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.04791506985794316</v>
+        <v>-0.04649155977863537</v>
       </c>
       <c r="AL14" t="n">
         <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.01902116456392708</v>
+        <v>0.3543369417923213</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0429206006035336</v>
+        <v>0.05007244057423758</v>
       </c>
       <c r="AP14" t="n">
         <v>-0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.01090408673582049</v>
+        <v>0.06633706570914172</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
@@ -7971,25 +7971,25 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.004345820832091814</v>
+        <v>0.6684302650791878</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1342668615451029</v>
+        <v>-0.0735242227101085</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0.07144544498884932</v>
+        <v>-0.188277960944885</v>
       </c>
       <c r="BD14" t="n">
         <v>-0</v>
@@ -7998,16 +7998,16 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.02620040164494168</v>
+        <v>-0.4060977161086732</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.06404054338065179</v>
+        <v>-0.5043999996521442</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
         <v>-0</v>
@@ -8016,52 +8016,52 @@
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0.04210517973425053</v>
+        <v>0.05659298679017785</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.09047894229518726</v>
+        <v>-0.2876631151057724</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.106944975261004</v>
+        <v>0.1029737308908746</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.03525699571751496</v>
+        <v>0.04350111613906527</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.053622043665989</v>
+        <v>0.6296382139647947</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.0892084166160886</v>
+        <v>0.2556384835767531</v>
       </c>
       <c r="BZ14" t="n">
         <v>-0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
@@ -8070,25 +8070,25 @@
         <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.02024200345559524</v>
+        <v>0.1009401090802098</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.004738800571421301</v>
+        <v>-0.3432665073873104</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.04866073733890929</v>
+        <v>0.08137684771100183</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
@@ -8097,52 +8097,52 @@
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.04424721686595955</v>
+        <v>0.03988697441777096</v>
       </c>
       <c r="CN14" t="n">
         <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.1287874322189005</v>
+        <v>-0.2987296044199825</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.1072087424960312</v>
+        <v>0.3959536617151789</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
         <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0.03365492003936697</v>
+        <v>0.08080334574033779</v>
       </c>
       <c r="CW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.03133483843755952</v>
+        <v>-0.3127658657830147</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.04856749824212982</v>
+        <v>0.04659358082348565</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
         <v>0</v>
@@ -8151,22 +8151,22 @@
         <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001738150906489228</v>
+        <v>-0.02371012097841244</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01553898703494556</v>
+        <v>-0.2147656660045498</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.0009489611483041381</v>
+        <v>0.01932067129339462</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,37 +8175,37 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.05051826818904669</v>
+        <v>0.113067773004762</v>
       </c>
       <c r="DO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.02220696297839628</v>
+        <v>-0.001621671958765586</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.09002526560996099</v>
+        <v>0.2103110334476115</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
         <v>0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.05315151116357613</v>
+        <v>0.1074976490144791</v>
       </c>
       <c r="DX14" t="n">
         <v>0</v>
@@ -8214,70 +8214,70 @@
         <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.007786335718453534</v>
+        <v>-0.1515583062902565</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.10340197342036</v>
+        <v>0.05054718723640533</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.007897586781982895</v>
+        <v>0.002363549485167613</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.03186369612230297</v>
+        <v>-0.3499461527882021</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.05226110065541255</v>
+        <v>-0.04443876927542193</v>
       </c>
       <c r="EK14" t="n">
         <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0.04698443825417613</v>
+        <v>-0.01859828741113046</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.02350287377671716</v>
+        <v>-0.3016439465460971</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01643504725067189</v>
+        <v>-0.06613813632539507</v>
       </c>
       <c r="ET14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
         <v>-0</v>
@@ -8286,46 +8286,46 @@
         <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.02774096773463049</v>
+        <v>0.1078815528239408</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.02204613115125234</v>
+        <v>-0.3986760472727282</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.04055711567018578</v>
+        <v>0.06449753814962375</v>
       </c>
       <c r="FC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0656241558314202</v>
+        <v>0.004915446715259883</v>
       </c>
       <c r="FH14" t="n">
         <v>-0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>-0.02509321085701874</v>
+        <v>-0.1581442754743611</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.09904040852698046</v>
+        <v>-0.06357179161691852</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8334,40 +8334,40 @@
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0.0003977485266464727</v>
+        <v>-0.1267100132128599</v>
       </c>
       <c r="FQ14" t="n">
         <v>0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.1076283148378972</v>
+        <v>-0.2716375634485062</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.0430848573884073</v>
+        <v>-0.08028248200615375</v>
       </c>
       <c r="FU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0.0317907133393224</v>
+        <v>0.03881117804297946</v>
       </c>
       <c r="FZ14" t="n">
         <v>-0</v>
@@ -8376,7 +8376,7 @@
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.08796926456126053</v>
+        <v>-0.3585287783874818</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
@@ -8396,25 +8396,25 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.07129228979941374</v>
+        <v>0.3071254560783389</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07581255442873253</v>
+        <v>0.07083764025496622</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.003776337527081642</v>
+        <v>-0.03395210486311245</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
@@ -8423,76 +8423,76 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.07857747991359448</v>
+        <v>0.312514353330599</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.04681773852492057</v>
+        <v>-0.08771670175962881</v>
       </c>
       <c r="O15" t="n">
-        <v>0.003173182458989264</v>
+        <v>0.05773037726831764</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.002088002906465035</v>
+        <v>-0.07889771786049132</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.01386425850623122</v>
+        <v>0.007352669098153792</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01232165621157259</v>
+        <v>-0.03490822825288369</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.0007253856974697618</v>
+        <v>0.01574665549206353</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01270329917678701</v>
+        <v>-0.1186677041666964</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.000281050422865</v>
+        <v>0.04994020411165105</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -8501,25 +8501,25 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.008780766025497419</v>
+        <v>0.02216773644915224</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.003803160775196672</v>
+        <v>-0.04087250078240472</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.008772719643667796</v>
+        <v>0.01965275246496824</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -8531,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.02445315430126497</v>
+        <v>0.01003749847860566</v>
       </c>
       <c r="AU15" t="n">
         <v>-0</v>
@@ -8543,10 +8543,10 @@
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.07483276810584058</v>
+        <v>0.01506334226035954</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.01360871841876834</v>
+        <v>-0.1039567481091139</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.01947860098977493</v>
+        <v>0.1186767475418153</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -8567,43 +8567,43 @@
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.00109296108167608</v>
+        <v>-0.02963882326982507</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.0009668649730723392</v>
+        <v>0.02082004080932206</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.006597581062686835</v>
+        <v>0.02047270345589522</v>
       </c>
       <c r="BM15" t="n">
         <v>-0</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.0183086812535305</v>
+        <v>-0.02502526090365034</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.009896865779509531</v>
+        <v>0.04765951592690405</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
@@ -8612,7 +8612,7 @@
         <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.01781998092415035</v>
+        <v>0.04844211668643235</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -8624,25 +8624,25 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.02858772287139641</v>
+        <v>-0.1571950588491225</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.008524393151670681</v>
+        <v>-0.06146482789422039</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0.01318387719417386</v>
+        <v>-0.07870225373765018</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF15" t="n">
         <v>-0</v>
@@ -8651,52 +8651,52 @@
         <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0146895537992623</v>
+        <v>0.03815808429554067</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01070148916902053</v>
+        <v>0.05426213087056927</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.005886519839791905</v>
+        <v>-0.02678757063344982</v>
       </c>
       <c r="CN15" t="n">
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.01864881254237221</v>
+        <v>0.1956031978905012</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.001070104031170792</v>
+        <v>-0.05820892478547596</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0.01126667360498811</v>
+        <v>-0.06854930424597794</v>
       </c>
       <c r="CW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX15" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.01358048131946878</v>
+        <v>0.01891316081017806</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01227720411082153</v>
+        <v>0.07393377192881694</v>
       </c>
       <c r="DB15" t="n">
         <v>-0</v>
@@ -8720,88 +8720,88 @@
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>-0.003200759082367356</v>
+        <v>-0.01842055133695638</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.02403572018532018</v>
+        <v>-0.2147378919228628</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.003051516122961599</v>
+        <v>-0.01290626413400959</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.0007621655144813144</v>
+        <v>0.01714021063796024</v>
       </c>
       <c r="DO15" t="n">
         <v>0</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ15" t="n">
         <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.01717235574941413</v>
+        <v>0.09145334607742905</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.02116918835979225</v>
+        <v>0.03426355101934238</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0.002858002726239097</v>
+        <v>0.03509822916771728</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY15" t="n">
         <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01310465504136489</v>
+        <v>0.141211021177271</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.003606351526593144</v>
+        <v>0.08483837318406837</v>
       </c>
       <c r="EC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0.01875675202308047</v>
+        <v>0.03778525248987515</v>
       </c>
       <c r="EG15" t="n">
         <v>0</v>
@@ -8813,10 +8813,10 @@
         <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.0003196736529579907</v>
+        <v>-0.02212305225820896</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0.01154406568450632</v>
+        <v>-0.07700300145732702</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
@@ -8828,22 +8828,22 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0.01204143393626208</v>
+        <v>-0.01464507105233418</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.002885573935629679</v>
+        <v>-0.0108542847103653</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.006816339416572323</v>
+        <v>-0.01088715951709817</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
@@ -8852,13 +8852,13 @@
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>-0.01241257355674662</v>
+        <v>-0.05053509063242097</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
@@ -8867,64 +8867,64 @@
         <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01513512419395737</v>
+        <v>0.01124038773615787</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01367696027708793</v>
+        <v>0.07449327013978532</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.004337711884879534</v>
+        <v>-0.2011915931265671</v>
       </c>
       <c r="FH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.001126480690119104</v>
+        <v>0.1561223922449268</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0.001380008776357887</v>
+        <v>0.01620060248708003</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.01076773567183804</v>
+        <v>-0.1710047651770671</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.004503765421043308</v>
+        <v>0.04431593523592669</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.01043186732191912</v>
+        <v>0.1019818927055032</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
@@ -8933,13 +8933,13 @@
         <v>-0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.005702496142032789</v>
+        <v>0.05435877217855771</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.008260586913584739</v>
+        <v>0.07141891577730974</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
